--- a/results/random_forest/quality_error_report.xlsx
+++ b/results/random_forest/quality_error_report.xlsx
@@ -456,14 +456,14 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>47232.5</v>
+        <v>46837.7906139714</v>
       </c>
       <c r="D2" t="n">
-        <v>47232.5</v>
+        <v>46837.7906139714</v>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
-        <v>133.7614341140155</v>
+        <v>132.643625538703</v>
       </c>
     </row>
     <row r="3">
@@ -474,16 +474,16 @@
         <v>17</v>
       </c>
       <c r="C3" t="n">
-        <v>17125.88647058824</v>
+        <v>17401.72413343404</v>
       </c>
       <c r="D3" t="n">
-        <v>23119.24735999105</v>
+        <v>23291.09724029938</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3993614467097532</v>
+        <v>0.3903989326766689</v>
       </c>
       <c r="F3" t="n">
-        <v>22.04229375773992</v>
+        <v>22.23128984602752</v>
       </c>
     </row>
     <row r="4">
@@ -494,36 +494,36 @@
         <v>4</v>
       </c>
       <c r="C4" t="n">
-        <v>12768.9375</v>
+        <v>11381.53443363588</v>
       </c>
       <c r="D4" t="n">
-        <v>16266.60492437266</v>
+        <v>15361.09874690266</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4499422232872506</v>
+        <v>0.5094773866950236</v>
       </c>
       <c r="F4" t="n">
-        <v>16.06308943507955</v>
+        <v>14.3414508196803</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="C5" t="n">
-        <v>45864.845</v>
+        <v>25770.43090755009</v>
       </c>
       <c r="D5" t="n">
-        <v>62455.89563230532</v>
+        <v>37491.19167200676</v>
       </c>
       <c r="E5" t="n">
-        <v>0.07126930429635681</v>
+        <v>0.4987267709294344</v>
       </c>
       <c r="F5" t="n">
-        <v>10.56849018283521</v>
+        <v>9.743683243840582</v>
       </c>
     </row>
     <row r="6">
@@ -534,36 +534,36 @@
         <v>56</v>
       </c>
       <c r="C6" t="n">
-        <v>11220.87178571429</v>
+        <v>10661.0706827829</v>
       </c>
       <c r="D6" t="n">
-        <v>16303.77926704551</v>
+        <v>15584.44713901533</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6097150999700891</v>
+        <v>0.6433945505323755</v>
       </c>
       <c r="F6" t="n">
-        <v>10.06749098277687</v>
+        <v>9.702027139649909</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B7" t="n">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>26330.54793103448</v>
+        <v>39789.38938826716</v>
       </c>
       <c r="D7" t="n">
-        <v>37238.48520855259</v>
+        <v>54106.84336346644</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5054615829141842</v>
+        <v>0.3029766714316522</v>
       </c>
       <c r="F7" t="n">
-        <v>9.915275965986442</v>
+        <v>9.152985854329115</v>
       </c>
     </row>
     <row r="8">
@@ -574,56 +574,56 @@
         <v>44</v>
       </c>
       <c r="C8" t="n">
-        <v>17969.22477272727</v>
+        <v>17631.3920742567</v>
       </c>
       <c r="D8" t="n">
-        <v>23683.49790446432</v>
+        <v>23840.02935270742</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6865084985934735</v>
+        <v>0.6823508828192956</v>
       </c>
       <c r="F8" t="n">
-        <v>8.198944841046826</v>
+        <v>7.973335335236277</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B9" t="n">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C9" t="n">
-        <v>30293.66285714285</v>
+        <v>10475.55559249802</v>
       </c>
       <c r="D9" t="n">
-        <v>36606.32097899525</v>
+        <v>14748.93959481512</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5397054815066882</v>
+        <v>0.7936175537943125</v>
       </c>
       <c r="F9" t="n">
-        <v>7.884054567777992</v>
+        <v>6.706383458647728</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="C10" t="n">
-        <v>10989.72345454546</v>
+        <v>25271.73238498747</v>
       </c>
       <c r="D10" t="n">
-        <v>15464.65143036285</v>
+        <v>31122.98828103692</v>
       </c>
       <c r="E10" t="n">
-        <v>0.7731016002403728</v>
+        <v>0.6672744018072316</v>
       </c>
       <c r="F10" t="n">
-        <v>6.943328000407829</v>
+        <v>6.537191959772137</v>
       </c>
     </row>
   </sheetData>
